--- a/Excel/UnitConfig.xlsx
+++ b/Excel/UnitConfig.xlsx
@@ -1,113 +1,99 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="18326"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20228"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitWork\ETSource\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{D6588A20-09A5-448A-BE18-26831D4F8A00}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28695" windowHeight="12630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
-  <si>
-    <t>名字</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>描述</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>位置</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>身高</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>体重</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>米克尔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>#测试说明</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试说明</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>带有强力攻击技能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Desc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Position</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Height</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Weight</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>long</t>
+  </si>
+  <si>
+    <t>登录签到</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ignRewardArr</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>[]</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0,40,0,80,00,120,140</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -115,11 +101,30 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
@@ -153,15 +158,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -223,7 +232,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -256,26 +265,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -308,23 +300,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -500,113 +475,90 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C3:I6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="C3:N6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="3.875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="28.75" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="3" style="2" customWidth="1"/>
+    <col min="2" max="2" width="3.875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="5" style="2" customWidth="1"/>
+    <col min="4" max="4" width="18.75" style="2" customWidth="1"/>
+    <col min="5" max="5" width="13.125" style="2" customWidth="1"/>
+    <col min="6" max="7" width="12.125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="14.375" style="2" customWidth="1"/>
+    <col min="10" max="11" width="15.75" style="2" customWidth="1"/>
+    <col min="12" max="12" width="13.75" style="2" customWidth="1"/>
+    <col min="13" max="13" width="17.875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="15.5" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="2" t="s">
+    <row r="3" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="D3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+    </row>
+    <row r="4" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="D4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+    </row>
+    <row r="5" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>4</v>
-      </c>
+      <c r="D5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
     </row>
-    <row r="4" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2" t="s">
+    <row r="6" spans="3:14" s="1" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>6</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="3:9" s="3" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="C6" s="3">
-        <v>1001</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="3">
-        <v>1</v>
-      </c>
-      <c r="H6" s="3">
-        <v>178</v>
-      </c>
-      <c r="I6" s="3">
-        <v>68</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Excel/UnitConfig.xlsx
+++ b/Excel/UnitConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitWork\ETSource\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{D6588A20-09A5-448A-BE18-26831D4F8A00}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{038D23B8-D84A-4237-84EC-63272D725FE0}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28695" windowHeight="12630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>id</t>
   </si>
@@ -69,6 +69,65 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>每天分享次数</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>hareMaxNum</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>nt</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>分享的奖励</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>hareRewardNum</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t>2</t>
     </r>
@@ -80,7 +139,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>0,40,0,80,00,120,140</t>
+      <t>0,40,0,80,100,120,140</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -89,7 +148,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -101,20 +160,8 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -125,6 +172,14 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
@@ -169,8 +224,8 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -501,8 +556,12 @@
       <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
+      <c r="E3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>9</v>
+      </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
@@ -519,8 +578,12 @@
       <c r="D4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
+      <c r="E4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
@@ -537,8 +600,12 @@
       <c r="D5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+      <c r="E5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
@@ -552,8 +619,14 @@
       <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>6</v>
+      <c r="D6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="1">
+        <v>5</v>
+      </c>
+      <c r="F6" s="1">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/UnitConfig.xlsx
+++ b/Excel/UnitConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitWork\ETSource\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{038D23B8-D84A-4237-84EC-63272D725FE0}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{4D08DC0A-46C0-4453-9883-999AC54ECE35}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28695" windowHeight="12630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -128,19 +128,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>0,40,0,80,100,120,140</t>
-    </r>
+    <t>20,40,60,80,100,120,140</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
